--- a/data/Org mapping.xlsx
+++ b/data/Org mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Live Dashboard\Client_DL_Rec_Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://j2w-my.sharepoint.com/personal/ashique_khan_joulestowatts_com/Documents/Desktop/Streamlit Dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904C7300-4C81-435D-AF65-929E1AD3B215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{904C7300-4C81-435D-AF65-929E1AD3B215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1772D121-1EA2-49CF-BED7-B6B02D1281A1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1234,7 +1234,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C268"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1265,7 +1264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1276,7 +1275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1287,7 +1286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1298,7 +1297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -1309,7 +1308,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1331,7 +1330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -1342,7 +1341,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -1364,7 +1363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1375,7 +1374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -1386,7 +1385,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -1397,7 +1396,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -1408,7 +1407,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -1419,7 +1418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
@@ -1430,7 +1429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>28</v>
       </c>
@@ -1441,7 +1440,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
@@ -1452,7 +1451,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
@@ -1463,7 +1462,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
@@ -1507,7 +1506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>36</v>
       </c>
@@ -1529,7 +1528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>38</v>
       </c>
@@ -1540,7 +1539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>39</v>
       </c>
@@ -1606,7 +1605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>45</v>
       </c>
@@ -1617,7 +1616,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>46</v>
       </c>
@@ -1628,7 +1627,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>47</v>
       </c>
@@ -1639,7 +1638,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>48</v>
       </c>
@@ -1650,7 +1649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>49</v>
       </c>
@@ -1661,7 +1660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>50</v>
       </c>
@@ -1672,7 +1671,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>51</v>
       </c>
@@ -1683,7 +1682,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>52</v>
       </c>
@@ -1694,7 +1693,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>53</v>
       </c>
@@ -1705,7 +1704,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>55</v>
       </c>
@@ -1714,7 +1713,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>56</v>
       </c>
@@ -1725,7 +1724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>57</v>
       </c>
@@ -1736,7 +1735,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>58</v>
       </c>
@@ -1747,7 +1746,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>59</v>
       </c>
@@ -1769,7 +1768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>61</v>
       </c>
@@ -1780,7 +1779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>62</v>
       </c>
@@ -1791,7 +1790,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>63</v>
       </c>
@@ -1813,7 +1812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>65</v>
       </c>
@@ -1835,7 +1834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>67</v>
       </c>
@@ -1844,7 +1843,7 @@
       </c>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>68</v>
       </c>
@@ -1853,7 +1852,7 @@
       </c>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>69</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>70</v>
       </c>
@@ -1873,7 +1872,7 @@
       </c>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>71</v>
       </c>
@@ -1882,7 +1881,7 @@
       </c>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>72</v>
       </c>
@@ -1891,7 +1890,7 @@
       </c>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>73</v>
       </c>
@@ -1900,7 +1899,7 @@
       </c>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>74</v>
       </c>
@@ -1909,7 +1908,7 @@
       </c>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>75</v>
       </c>
@@ -1973,7 +1972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>81</v>
       </c>
@@ -1993,7 +1992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>83</v>
       </c>
@@ -2004,7 +2003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>84</v>
       </c>
@@ -2026,7 +2025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>86</v>
       </c>
@@ -2048,7 +2047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>88</v>
       </c>
@@ -2070,7 +2069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>90</v>
       </c>
@@ -2081,7 +2080,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>92</v>
       </c>
@@ -2092,7 +2091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>93</v>
       </c>
@@ -2125,7 +2124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>96</v>
       </c>
@@ -2136,7 +2135,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>97</v>
       </c>
@@ -2147,7 +2146,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>98</v>
       </c>
@@ -2158,7 +2157,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>99</v>
       </c>
@@ -2178,7 +2177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>101</v>
       </c>
@@ -2189,7 +2188,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>102</v>
       </c>
@@ -2211,7 +2210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>104</v>
       </c>
@@ -2233,7 +2232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>106</v>
       </c>
@@ -2242,7 +2241,7 @@
       </c>
       <c r="C93" s="2"/>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>107</v>
       </c>
@@ -2253,7 +2252,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>108</v>
       </c>
@@ -2264,7 +2263,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>109</v>
       </c>
@@ -2306,7 +2305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>113</v>
       </c>
@@ -2317,7 +2316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>114</v>
       </c>
@@ -2328,7 +2327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>115</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>116</v>
       </c>
@@ -2350,7 +2349,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>117</v>
       </c>
@@ -2372,7 +2371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>119</v>
       </c>
@@ -2427,7 +2426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>124</v>
       </c>
@@ -2482,7 +2481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>129</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>135</v>
       </c>
@@ -2559,7 +2558,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>136</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>137</v>
       </c>
@@ -2581,7 +2580,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>138</v>
       </c>
@@ -2592,7 +2591,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>139</v>
       </c>
@@ -2603,7 +2602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>140</v>
       </c>
@@ -2636,7 +2635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>143</v>
       </c>
@@ -2647,7 +2646,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>144</v>
       </c>
@@ -2713,7 +2712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>150</v>
       </c>
@@ -2724,7 +2723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>151</v>
       </c>
@@ -2735,7 +2734,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>152</v>
       </c>
@@ -2746,7 +2745,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>153</v>
       </c>
@@ -2757,7 +2756,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>154</v>
       </c>
@@ -2768,7 +2767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>155</v>
       </c>
@@ -2790,7 +2789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>157</v>
       </c>
@@ -2801,7 +2800,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>158</v>
       </c>
@@ -2812,7 +2811,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>159</v>
       </c>
@@ -2823,7 +2822,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>161</v>
       </c>
@@ -2834,7 +2833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>162</v>
       </c>
@@ -2845,7 +2844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>163</v>
       </c>
@@ -2922,7 +2921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>170</v>
       </c>
@@ -2933,7 +2932,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>171</v>
       </c>
@@ -2955,7 +2954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>173</v>
       </c>
@@ -2966,7 +2965,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>174</v>
       </c>
@@ -2977,7 +2976,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>175</v>
       </c>
@@ -2988,7 +2987,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>176</v>
       </c>
@@ -2999,7 +2998,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>177</v>
       </c>
@@ -3010,7 +3009,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>178</v>
       </c>
@@ -3021,7 +3020,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>179</v>
       </c>
@@ -3032,7 +3031,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>180</v>
       </c>
@@ -3043,7 +3042,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>181</v>
       </c>
@@ -3054,7 +3053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>182</v>
       </c>
@@ -3065,7 +3064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>183</v>
       </c>
@@ -3087,7 +3086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>185</v>
       </c>
@@ -3109,7 +3108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>187</v>
       </c>
@@ -3131,7 +3130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>189</v>
       </c>
@@ -3142,7 +3141,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>190</v>
       </c>
@@ -3186,7 +3185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>194</v>
       </c>
@@ -3197,7 +3196,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>196</v>
       </c>
@@ -3208,7 +3207,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>197</v>
       </c>
@@ -3219,7 +3218,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>198</v>
       </c>
@@ -3241,7 +3240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>200</v>
       </c>
@@ -3252,7 +3251,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>201</v>
       </c>
@@ -3263,7 +3262,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>202</v>
       </c>
@@ -3274,7 +3273,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>203</v>
       </c>
@@ -3296,7 +3295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>205</v>
       </c>
@@ -3307,7 +3306,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>206</v>
       </c>
@@ -3318,7 +3317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>207</v>
       </c>
@@ -3340,7 +3339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>209</v>
       </c>
@@ -3351,7 +3350,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>210</v>
       </c>
@@ -3362,7 +3361,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>211</v>
       </c>
@@ -3384,7 +3383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>213</v>
       </c>
@@ -3428,7 +3427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>217</v>
       </c>
@@ -3439,7 +3438,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>218</v>
       </c>
@@ -3450,7 +3449,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>219</v>
       </c>
@@ -3461,7 +3460,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>220</v>
       </c>
@@ -3472,7 +3471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>221</v>
       </c>
@@ -3494,7 +3493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>223</v>
       </c>
@@ -3505,7 +3504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>224</v>
       </c>
@@ -3516,7 +3515,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>225</v>
       </c>
@@ -3527,7 +3526,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>226</v>
       </c>
@@ -3538,7 +3537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>227</v>
       </c>
@@ -3549,7 +3548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>228</v>
       </c>
@@ -3560,7 +3559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>229</v>
       </c>
@@ -3571,7 +3570,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>230</v>
       </c>
@@ -3582,7 +3581,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>231</v>
       </c>
@@ -3593,7 +3592,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>232</v>
       </c>
@@ -3604,7 +3603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>233</v>
       </c>
@@ -3615,7 +3614,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>234</v>
       </c>
@@ -3637,7 +3636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>236</v>
       </c>
@@ -3659,7 +3658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>238</v>
       </c>
@@ -3692,7 +3691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>241</v>
       </c>
@@ -3703,7 +3702,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>242</v>
       </c>
@@ -3714,7 +3713,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>243</v>
       </c>
@@ -3725,7 +3724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>244</v>
       </c>
@@ -3736,7 +3735,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>245</v>
       </c>
@@ -3747,7 +3746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>246</v>
       </c>
@@ -3758,7 +3757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>247</v>
       </c>
@@ -3835,7 +3834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>254</v>
       </c>
@@ -3857,7 +3856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>257</v>
       </c>
@@ -3868,7 +3867,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>258</v>
       </c>
@@ -3890,7 +3889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>260</v>
       </c>
@@ -3901,7 +3900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>261</v>
       </c>
@@ -3912,7 +3911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>262</v>
       </c>
@@ -3923,7 +3922,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>263</v>
       </c>
@@ -3934,7 +3933,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>264</v>
       </c>
@@ -3945,7 +3944,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>265</v>
       </c>
@@ -3956,7 +3955,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>266</v>
       </c>
@@ -3989,7 +3988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>269</v>
       </c>
@@ -4033,7 +4032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>273</v>
       </c>
@@ -4077,7 +4076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>277</v>
       </c>
@@ -4099,7 +4098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>279</v>
       </c>
@@ -4110,7 +4109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>280</v>
       </c>
@@ -4121,42 +4120,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>284</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C268" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Captive"/>
-        <filter val="Services"/>
-        <filter val="SOW Captive"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Deepak Desai"/>
-        <filter val="Deepak Desai Non IT"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Org mapping.xlsx
+++ b/data/Org mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://j2w-my.sharepoint.com/personal/ashique_khan_joulestowatts_com/Documents/Desktop/Streamlit Dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{904C7300-4C81-435D-AF65-929E1AD3B215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1772D121-1EA2-49CF-BED7-B6B02D1281A1}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{904C7300-4C81-435D-AF65-929E1AD3B215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F20F9484-A090-465A-A879-B09FC55B29C3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,16 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="285">
-  <si>
-    <t>domain</t>
-  </si>
-  <si>
-    <t>business_head</t>
-  </si>
-  <si>
-    <t>client</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="288">
   <si>
     <t>DAMAC</t>
   </si>
@@ -74,9 +65,6 @@
     <t>ITES</t>
   </si>
   <si>
-    <t>Jawad Ulla Khan Non IT</t>
-  </si>
-  <si>
     <t>Toyota</t>
   </si>
   <si>
@@ -110,9 +98,6 @@
     <t>Akkodis</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>Alliance Data</t>
   </si>
   <si>
@@ -203,9 +188,6 @@
     <t>RealPage</t>
   </si>
   <si>
-    <t>Deepak Desai Non IT</t>
-  </si>
-  <si>
     <t>VISA</t>
   </si>
   <si>
@@ -521,9 +503,6 @@
     <t xml:space="preserve">Lumen routing </t>
   </si>
   <si>
-    <t>Anuradha Murthy Non IT</t>
-  </si>
-  <si>
     <t>Medline</t>
   </si>
   <si>
@@ -894,13 +873,43 @@
   </si>
   <si>
     <t>Infosys 3</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>BH Tag</t>
+  </si>
+  <si>
+    <t>Nirmit Desai</t>
+  </si>
+  <si>
+    <t>Jawad Ulla Khan</t>
+  </si>
+  <si>
+    <t>Tarun Sareen</t>
+  </si>
+  <si>
+    <t>Aashis Ranjan</t>
+  </si>
+  <si>
+    <t>Unassigned</t>
+  </si>
+  <si>
+    <t>sadhna Shukla</t>
+  </si>
+  <si>
+    <t>Kiran SiddheGowda</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -908,8 +917,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -922,8 +951,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -946,19 +999,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1234,524 +1521,526 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C268"/>
+  <dimension ref="A1:C273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
+      <c r="A1" s="3" t="s">
+        <v>278</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="B3" s="2">
         <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
+      <c r="A4" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>22</v>
+      <c r="A13" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>23</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>24</v>
+      <c r="A14" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="B14" s="2" t="e">
         <v>#N/A</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="B22" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>35</v>
+      <c r="A24" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>37</v>
+      <c r="A26" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>38</v>
+      <c r="A27" s="15" t="s">
+        <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>40</v>
+      <c r="A29" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>43</v>
+      <c r="A32" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>46</v>
+      <c r="A35" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>47</v>
+      <c r="A36" s="16" t="s">
+        <v>42</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="B42" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>54</v>
+        <v>281</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>17</v>
@@ -1759,1284 +2048,1300 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>62</v>
+      <c r="A50" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>65</v>
+      <c r="A53" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>5</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B56" s="2">
         <v>0</v>
       </c>
-      <c r="C56" s="2"/>
+      <c r="C56" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B57" s="2">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>23</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B58" s="2">
         <v>0</v>
       </c>
-      <c r="C58" s="2"/>
+      <c r="C58" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B59" s="2">
         <v>0</v>
       </c>
-      <c r="C59" s="2"/>
+      <c r="C59" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B60" s="2">
         <v>0</v>
       </c>
-      <c r="C60" s="2"/>
+      <c r="C60" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B61" s="2">
         <v>0</v>
       </c>
-      <c r="C61" s="2"/>
+      <c r="C61" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B62" s="2">
         <v>0</v>
       </c>
-      <c r="C62" s="2"/>
+      <c r="C62" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B63" s="2">
-        <v>0</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B63" s="2"/>
       <c r="C63" s="2"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>76</v>
+      <c r="A64" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>78</v>
+      <c r="A66" s="11" t="s">
+        <v>72</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>79</v>
+      <c r="A67" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>80</v>
+      <c r="A68" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>81</v>
+      <c r="A69" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>84</v>
+      <c r="A72" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>5</v>
+        <v>285</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>87</v>
+      <c r="A75" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B79" s="2">
-        <v>0</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="B83" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>99</v>
+      <c r="A86" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>100</v>
+      <c r="A87" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>103</v>
+      <c r="A90" s="11" t="s">
+        <v>97</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>106</v>
+      <c r="A93" s="11" t="s">
+        <v>100</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C93" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>23</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>109</v>
+      <c r="A96" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
+      <c r="B103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
+      <c r="B104" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="B105" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>120</v>
+      <c r="A107" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
-        <v>122</v>
+      <c r="A109" s="11" t="s">
+        <v>116</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
-        <v>123</v>
+      <c r="A110" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
-        <v>124</v>
+      <c r="A111" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
-        <v>125</v>
+      <c r="A112" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>5</v>
+        <v>285</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>126</v>
+      <c r="A113" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
-        <v>128</v>
+      <c r="A115" s="11" t="s">
+        <v>122</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
-        <v>129</v>
+      <c r="A116" s="11" t="s">
+        <v>123</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
-        <v>130</v>
+      <c r="A117" s="11" t="s">
+        <v>124</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
-        <v>131</v>
+      <c r="A118" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>54</v>
+        <v>283</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>5</v>
+        <v>248</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
+      <c r="B128" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
+      <c r="B129" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
+      <c r="B130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="B131" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
-        <v>148</v>
+      <c r="A135" s="7" t="s">
+        <v>142</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
-        <v>149</v>
+      <c r="A136" s="7" t="s">
+        <v>143</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
-        <v>150</v>
+      <c r="A137" s="16" t="s">
+        <v>144</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>11</v>
+        <v>282</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>11</v>
+        <v>282</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>153</v>
+      <c r="A140" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="2" t="s">
-        <v>155</v>
+      <c r="A142" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="2" t="s">
-        <v>159</v>
+      <c r="A146" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="2" t="s">
-        <v>161</v>
+      <c r="A147" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>11</v>
+        <v>285</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>11</v>
+        <v>285</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="2" t="s">
-        <v>163</v>
+      <c r="A149" s="7" t="s">
+        <v>156</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="2" t="s">
-        <v>164</v>
+      <c r="A150" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="2" t="s">
-        <v>169</v>
+      <c r="A155" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="2" t="s">
-        <v>170</v>
+      <c r="A156" s="11" t="s">
+        <v>163</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>29</v>
+        <v>285</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="2" t="s">
-        <v>171</v>
+      <c r="A157" s="15" t="s">
+        <v>164</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="2" t="s">
-        <v>174</v>
+      <c r="A160" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="2" t="s">
-        <v>175</v>
+      <c r="A161" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="2" t="s">
-        <v>178</v>
+      <c r="A164" s="7" t="s">
+        <v>171</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>17</v>
@@ -3044,1103 +3349,1137 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="2" t="s">
-        <v>182</v>
+      <c r="A168" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>23</v>
+        <v>284</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>23</v>
+        <v>284</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="2" t="s">
-        <v>189</v>
+      <c r="A175" s="11" t="s">
+        <v>182</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="2" t="s">
-        <v>190</v>
+      <c r="A176" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="2" t="s">
-        <v>191</v>
+      <c r="A177" s="11" t="s">
+        <v>184</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="2" t="s">
-        <v>194</v>
+      <c r="A180" s="7" t="s">
+        <v>187</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>23</v>
+        <v>284</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="2" t="s">
-        <v>197</v>
+      <c r="A182" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>23</v>
+        <v>284</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="2" t="s">
-        <v>198</v>
+      <c r="A183" s="15" t="s">
+        <v>191</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
-        <v>202</v>
+      <c r="A187" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="2" t="s">
-        <v>203</v>
+      <c r="A188" s="11" t="s">
+        <v>196</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="2" t="s">
-        <v>204</v>
+      <c r="A189" s="5" t="s">
+        <v>197</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="B190" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="2" t="s">
+      <c r="B197" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="2" t="s">
+      <c r="B198" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="B192" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="2" t="s">
+      <c r="B199" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B193" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="2" t="s">
+      <c r="B200" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="2" t="s">
+      <c r="B201" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="2" t="s">
+      <c r="B202" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="2" t="s">
+      <c r="B203" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="2" t="s">
+      <c r="B204" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="2" t="s">
+      <c r="B205" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="2" t="s">
+      <c r="B206" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="2" t="s">
+      <c r="B207" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="B201" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="2" t="s">
+      <c r="B208" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="B202" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="B209" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="2" t="s">
-        <v>228</v>
+      <c r="A213" s="23" t="s">
+        <v>221</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>23</v>
+        <v>284</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="2" t="s">
-        <v>230</v>
+      <c r="A215" s="15" t="s">
+        <v>223</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="2" t="s">
-        <v>231</v>
+      <c r="A216" s="11" t="s">
+        <v>224</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>54</v>
+        <v>282</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="2" t="s">
-        <v>232</v>
+      <c r="A217" s="15" t="s">
+        <v>225</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="2" t="s">
-        <v>233</v>
+      <c r="A218" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>23</v>
+        <v>284</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="2" t="s">
-        <v>235</v>
+      <c r="A220" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="2" t="s">
-        <v>238</v>
+      <c r="A223" s="11" t="s">
+        <v>231</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
-        <v>240</v>
+      <c r="A225" s="11" t="s">
+        <v>233</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="2" t="s">
-        <v>241</v>
+      <c r="A226" s="7" t="s">
+        <v>234</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="2" t="s">
-        <v>244</v>
+      <c r="A229" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="2" t="s">
-        <v>245</v>
+      <c r="A230" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C230" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="2" t="s">
-        <v>247</v>
+      <c r="A232" s="14" t="s">
+        <v>240</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>23</v>
+        <v>287</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="B242" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="2" t="s">
+      <c r="B249" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B243" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="B250" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="2" t="s">
-        <v>268</v>
+      <c r="A252" s="14" t="s">
+        <v>261</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="2" t="s">
-        <v>269</v>
+      <c r="A253" s="15" t="s">
+        <v>262</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="2" t="s">
-        <v>270</v>
+      <c r="A254" s="11" t="s">
+        <v>263</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="2" t="s">
-        <v>277</v>
+      <c r="A261" s="14" t="s">
+        <v>270</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="2" t="s">
-        <v>278</v>
+      <c r="A262" s="14" t="s">
+        <v>271</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>5</v>
+        <v>281</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="2" t="s">
-        <v>279</v>
+      <c r="A263" s="5" t="s">
+        <v>272</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C263" s="2"/>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B264" s="2">
-        <v>0</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="B264" s="2"/>
+      <c r="C264" s="2"/>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>281</v>
+      <c r="A265" s="2" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>282</v>
+      <c r="A266" s="25" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>283</v>
+      <c r="A267" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B267" t="s">
+        <v>15</v>
+      </c>
+      <c r="C267" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>284</v>
-      </c>
+      <c r="A268" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" s="26"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A235">
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A238:A240">
+    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A261:A262">
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A263 A227:A234 A241:A242 A1:A49 A51:A225 A268:A1048576">
+    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A264">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A265">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A266">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A267">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Org mapping.xlsx
+++ b/data/Org mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://j2w-my.sharepoint.com/personal/ashique_khan_joulestowatts_com/Documents/Desktop/Streamlit Dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{904C7300-4C81-435D-AF65-929E1AD3B215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F20F9484-A090-465A-A879-B09FC55B29C3}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{904C7300-4C81-435D-AF65-929E1AD3B215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C46F55D-1C13-4B3D-983E-2788CDDBC775}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="291">
   <si>
     <t>DAMAC</t>
   </si>
@@ -884,25 +884,34 @@
     <t>BH Tag</t>
   </si>
   <si>
-    <t>Nirmit Desai</t>
-  </si>
-  <si>
     <t>Jawad Ulla Khan</t>
   </si>
   <si>
-    <t>Tarun Sareen</t>
-  </si>
-  <si>
     <t>Aashis Ranjan</t>
   </si>
   <si>
-    <t>Unassigned</t>
-  </si>
-  <si>
-    <t>sadhna Shukla</t>
-  </si>
-  <si>
-    <t>Kiran SiddheGowda</t>
+    <t>Jawad Ulla Khan Non IT</t>
+  </si>
+  <si>
+    <t>Mher</t>
+  </si>
+  <si>
+    <t>Deepak Desai Non IT</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Mher Non IT</t>
+  </si>
+  <si>
+    <t>Ashok shastry</t>
+  </si>
+  <si>
+    <t>Anuradha Murthy Non IT</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1557,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1559,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1570,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1581,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1592,7 +1601,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1603,7 +1612,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1614,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1625,7 +1634,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1647,7 +1656,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1658,7 +1667,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1669,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1679,8 +1688,8 @@
       <c r="B14" s="2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>13</v>
+      <c r="C14" s="2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1691,7 +1700,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>24</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1702,7 +1711,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1713,7 +1722,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1724,7 +1733,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1735,7 +1744,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1746,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1768,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1779,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1790,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1812,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1845,7 +1854,7 @@
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1856,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1867,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1878,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1889,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1933,7 +1942,7 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1944,7 +1953,7 @@
         <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1955,7 +1964,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1988,7 +1997,7 @@
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1999,7 +2008,7 @@
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2032,7 +2041,7 @@
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2043,7 +2052,7 @@
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2087,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2098,7 +2107,7 @@
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2109,7 +2118,7 @@
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2120,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>284</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2131,7 +2140,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>284</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2142,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2153,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2164,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2175,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2186,7 +2195,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2197,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2208,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2216,7 +2225,9 @@
         <v>69</v>
       </c>
       <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
+      <c r="C63" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
@@ -2226,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2237,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2248,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2259,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2270,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2281,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2292,7 +2303,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2303,7 +2314,7 @@
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2314,7 +2325,7 @@
         <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>285</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2325,7 +2336,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2347,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2369,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2388,7 +2399,9 @@
         <v>86</v>
       </c>
       <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
+      <c r="C79" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="18" t="s">
@@ -2398,7 +2411,7 @@
         <v>1</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2409,7 +2422,7 @@
         <v>15</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2420,7 +2433,7 @@
         <v>15</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2442,7 +2455,7 @@
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2453,7 +2466,7 @@
         <v>12</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2464,7 +2477,7 @@
         <v>15</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2475,7 +2488,7 @@
         <v>15</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2497,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2508,7 +2521,7 @@
         <v>15</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2519,7 +2532,7 @@
         <v>12</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2530,7 +2543,7 @@
         <v>15</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -2541,7 +2554,7 @@
         <v>15</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -2563,7 +2576,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2574,7 +2587,7 @@
         <v>15</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2585,7 +2598,7 @@
         <v>15</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2596,7 +2609,7 @@
         <v>15</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2607,7 +2620,7 @@
         <v>15</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2618,7 +2631,7 @@
         <v>12</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2629,7 +2642,7 @@
         <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2640,7 +2653,7 @@
         <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2651,7 +2664,7 @@
         <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2662,7 +2675,7 @@
         <v>7</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -2695,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2750,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>285</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -2794,7 +2807,7 @@
         <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>2</v>
+        <v>285</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -2805,7 +2818,7 @@
         <v>1</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -2816,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -2827,7 +2840,7 @@
         <v>12</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -2838,7 +2851,7 @@
         <v>12</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -2849,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -2860,7 +2873,7 @@
         <v>12</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>281</v>
+        <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -2904,7 +2917,7 @@
         <v>7</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>282</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -2915,7 +2928,7 @@
         <v>7</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2926,7 +2939,7 @@
         <v>1</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -2937,7 +2950,7 @@
         <v>12</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -2948,7 +2961,7 @@
         <v>12</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -2970,7 +2983,7 @@
         <v>12</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -2981,7 +2994,7 @@
         <v>1</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -2992,7 +3005,7 @@
         <v>1</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3003,7 +3016,7 @@
         <v>12</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3014,7 +3027,7 @@
         <v>12</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3036,7 +3049,7 @@
         <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3047,7 +3060,7 @@
         <v>7</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3069,7 +3082,7 @@
         <v>12</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3080,7 +3093,7 @@
         <v>1</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3091,7 +3104,7 @@
         <v>1</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3124,7 +3137,7 @@
         <v>7</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>24</v>
+        <v>290</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3135,7 +3148,7 @@
         <v>1</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3146,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3157,7 +3170,7 @@
         <v>7</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>2</v>
+        <v>283</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3168,7 +3181,7 @@
         <v>1</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3179,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3190,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3201,7 +3214,7 @@
         <v>1</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3212,7 +3225,7 @@
         <v>1</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3223,7 +3236,7 @@
         <v>1</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3233,8 +3246,8 @@
       <c r="B156" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C156" s="2" t="s">
-        <v>285</v>
+      <c r="C156" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3256,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3300,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>24</v>
+        <v>290</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -3333,7 +3346,7 @@
         <v>1</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>24</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -3344,7 +3357,7 @@
         <v>12</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -3355,7 +3368,7 @@
         <v>1</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -3366,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -3377,7 +3390,7 @@
         <v>1</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -3388,7 +3401,7 @@
         <v>1</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -3399,7 +3412,7 @@
         <v>12</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -3410,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -3432,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -3443,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -3465,7 +3478,7 @@
         <v>1</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -3476,7 +3489,7 @@
         <v>1</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -3487,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -3509,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -3520,7 +3533,7 @@
         <v>12</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -3542,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -3553,7 +3566,7 @@
         <v>12</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -3564,7 +3577,7 @@
         <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>24</v>
+        <v>290</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -3597,7 +3610,7 @@
         <v>1</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -3608,7 +3621,7 @@
         <v>15</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>17</v>
+        <v>284</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -3619,7 +3632,7 @@
         <v>7</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -3641,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -3652,7 +3665,7 @@
         <v>7</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>286</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -3663,7 +3676,7 @@
         <v>7</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>283</v>
+        <v>24</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -3685,7 +3698,7 @@
         <v>1</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -3696,7 +3709,7 @@
         <v>12</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -3707,7 +3720,7 @@
         <v>1</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -3718,7 +3731,7 @@
         <v>1</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -3729,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -3740,7 +3753,7 @@
         <v>7</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -3751,7 +3764,7 @@
         <v>7</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -3795,7 +3808,7 @@
         <v>1</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -3817,7 +3830,7 @@
         <v>7</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -3828,7 +3841,7 @@
         <v>7</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -3839,7 +3852,7 @@
         <v>7</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -3850,7 +3863,7 @@
         <v>7</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -3861,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -3894,7 +3907,7 @@
         <v>7</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -3916,7 +3929,7 @@
         <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -3938,7 +3951,7 @@
         <v>1</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -3949,7 +3962,7 @@
         <v>7</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -3960,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -3971,7 +3984,7 @@
         <v>7</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -3982,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -3993,7 +4006,7 @@
         <v>12</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4036,8 +4049,8 @@
       <c r="B229" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C229" s="2" t="s">
-        <v>13</v>
+      <c r="C229" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4048,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4081,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4092,7 +4105,7 @@
         <v>1</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4103,7 +4116,7 @@
         <v>1</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4114,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4125,7 +4138,7 @@
         <v>1</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4136,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4147,7 +4160,7 @@
         <v>1</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4158,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4169,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4180,7 +4193,7 @@
         <v>1</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4191,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4202,7 +4215,7 @@
         <v>7</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4279,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -4290,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -4301,7 +4314,7 @@
         <v>12</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -4312,7 +4325,7 @@
         <v>1</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -4323,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -4334,7 +4347,7 @@
         <v>1</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -4345,7 +4358,7 @@
         <v>7</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>2</v>
+        <v>290</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -4356,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -4367,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -4378,7 +4391,7 @@
         <v>1</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -4389,7 +4402,7 @@
         <v>7</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -4400,7 +4413,7 @@
         <v>1</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -4410,24 +4423,34 @@
       <c r="B263" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C263" s="2"/>
+      <c r="C263" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>273</v>
       </c>
       <c r="B264" s="2"/>
-      <c r="C264" s="2"/>
+      <c r="C264" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>274</v>
       </c>
+      <c r="C265" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="25" t="s">
         <v>275</v>
       </c>
+      <c r="C266" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
@@ -4437,7 +4460,7 @@
         <v>15</v>
       </c>
       <c r="C267" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
